--- a/data/cases/register_cases.xlsx
+++ b/data/cases/register_cases.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>13414764310</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
